--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104660_W23.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104660_W23.xlsx
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3978</v>
+        <v>5.844</v>
       </c>
       <c r="E2" t="n">
-        <v>5.777</v>
+        <v>6.2006</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3791</v>
+        <v>-0.3566</v>
       </c>
       <c r="G2" t="n">
-        <v>7.6873</v>
+        <v>7.6694</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8369</v>
+        <v>-0.8386</v>
       </c>
       <c r="I2" t="n">
-        <v>8.5242</v>
+        <v>8.507999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>8.4808</v>
+        <v>8.4399</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3952</v>
+        <v>-0.4072</v>
       </c>
       <c r="L2" t="n">
-        <v>8.875999999999999</v>
+        <v>8.847</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7935</v>
+        <v>-0.7704</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3517</v>
+        <v>-0.3391</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7017</v>
+        <v>-0.232</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2087</v>
+        <v>0.2647</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.493</v>
+        <v>-0.4967</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. GONZALEZ</t>
+          <t>D. ROBINSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8231</v>
+        <v>3.9927</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6204</v>
+        <v>5.6668</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2028</v>
+        <v>-1.6742</v>
       </c>
       <c r="G3" t="n">
-        <v>3.203</v>
+        <v>1.6987</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9320000000000001</v>
+        <v>1.4959</v>
       </c>
       <c r="I3" t="n">
-        <v>2.271</v>
+        <v>0.2028</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5197</v>
+        <v>3.7335</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9177999999999999</v>
+        <v>3.0337</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6019</v>
+        <v>0.6998</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6833</v>
+        <v>-2.0348</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0142</v>
+        <v>-1.5378</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6691</v>
+        <v>-0.497</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0169</v>
+        <v>-0.706</v>
       </c>
       <c r="T3" t="n">
-        <v>0.369</v>
+        <v>0.1414</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3859</v>
+        <v>-0.8474</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3176</v>
+        <v>1.6342</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.792</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2249</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. ROBINSON</t>
+          <t>M. GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6759</v>
+        <v>3.9405</v>
       </c>
       <c r="E4" t="n">
-        <v>5.575</v>
+        <v>2.8391</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8991</v>
+        <v>1.1015</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6848</v>
+        <v>3.2117</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4876</v>
+        <v>0.9415</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1973</v>
+        <v>2.2701</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7541</v>
+        <v>2.5071</v>
       </c>
       <c r="K4" t="n">
-        <v>3.0477</v>
+        <v>0.9136</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7063</v>
+        <v>1.5935</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0692</v>
+        <v>0.7046</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5602</v>
+        <v>0.028</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.509</v>
+        <v>0.6766</v>
       </c>
       <c r="P4" t="n">
-        <v>1.361</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.009</v>
+        <v>0.0931</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0212</v>
+        <v>0.6083</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0301</v>
+        <v>-0.5152</v>
       </c>
       <c r="V4" t="n">
-        <v>1.639</v>
+        <v>1.3187</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7997</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1607</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. DUBLJEVIC</t>
+          <t>M. SPISSU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4021</v>
+        <v>1.764</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2475</v>
+        <v>2.5007</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1545</v>
+        <v>-0.7366</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.8613</v>
+        <v>1.7508</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4055</v>
+        <v>-2.6778</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4558</v>
+        <v>4.4286</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.0848</v>
+        <v>3.358</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.333</v>
+        <v>-0.9243</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7517</v>
+        <v>4.2822</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7765</v>
+        <v>-1.6072</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0725</v>
+        <v>-1.7535</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2959</v>
+        <v>0.1463</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-3.4145</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2634</v>
+        <v>-0.7316</v>
       </c>
       <c r="T5" t="n">
-        <v>3.3057</v>
+        <v>0.3782</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0424</v>
+        <v>-1.1099</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>2.5659</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2534</v>
+        <v>2.1789</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1607</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. STEPHENS</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5455</v>
+        <v>1.4755</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3855</v>
+        <v>2.5342</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.84</v>
+        <v>-1.0586</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0014</v>
+        <v>1.5939</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0434</v>
+        <v>-0.1151</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0449</v>
+        <v>1.709</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5216</v>
+        <v>3.2406</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4373</v>
+        <v>1.1926</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0843</v>
+        <v>2.048</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.5202</v>
+        <v>-1.6467</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4807</v>
+        <v>-1.3077</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0395</v>
+        <v>-0.3391</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5878</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0437</v>
+        <v>-0.2761</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0907</v>
+        <v>0.5016</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1345</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. KOUMADJE</t>
+          <t>D. STEPHENS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0965</v>
+        <v>1.4665</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8068</v>
+        <v>3.2471</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7103</v>
+        <v>-1.7806</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7141999999999999</v>
+        <v>1.0077</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7648</v>
+        <v>-0.0349</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0506</v>
+        <v>1.0426</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0205</v>
+        <v>3.5006</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7966</v>
+        <v>1.4307</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2239</v>
+        <v>2.0699</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3063</v>
+        <v>-2.4929</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0318</v>
+        <v>-1.4656</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2745</v>
+        <v>-1.0273</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0213</v>
+        <v>-1.1346</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7864</v>
+        <v>-0.0258</v>
       </c>
       <c r="U7" t="n">
-        <v>0.235</v>
+        <v>-1.1088</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SPISSU</t>
+          <t>B. DUBLJEVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0323</v>
+        <v>1.3271</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1808</v>
+        <v>1.4515</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1485</v>
+        <v>-0.1244</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7344</v>
+        <v>-1.8576</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.6957</v>
+        <v>-1.4018</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4301</v>
+        <v>-0.4558</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3767</v>
+        <v>-1.1123</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9147</v>
+        <v>-0.3522</v>
       </c>
       <c r="L8" t="n">
-        <v>4.2914</v>
+        <v>-0.7601</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6424</v>
+        <v>-0.7453</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.781</v>
+        <v>-1.0496</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1387</v>
+        <v>0.3043</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4025</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4584</v>
+        <v>1.1847</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0212</v>
+        <v>1.5442</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.4796</v>
+        <v>-0.3595</v>
       </c>
       <c r="V8" t="n">
-        <v>2.571</v>
+        <v>1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1853</v>
+        <v>1.2472</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3856</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>C. KOUMADJE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9494</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8485</v>
+        <v>1.4506</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8991</v>
+        <v>-0.9188</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5823</v>
+        <v>0.7165</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1184</v>
+        <v>0.764</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7007</v>
+        <v>-0.0475</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2575</v>
+        <v>1.0163</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2051</v>
+        <v>0.7929</v>
       </c>
       <c r="L9" t="n">
-        <v>2.0524</v>
+        <v>0.2234</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6752</v>
+        <v>-0.2998</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3234</v>
+        <v>-0.0289</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3517</v>
+        <v>-0.271</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7936</v>
+        <v>0.4495</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2087</v>
+        <v>0.4343</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5849</v>
+        <v>0.0152</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1607</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.497</v>
+        <v>-1.4398</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5365</v>
+        <v>-0.4229</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0335</v>
+        <v>-1.0169</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0282</v>
+        <v>0.0311</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2308</v>
+        <v>0.2353</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2026</v>
+        <v>-0.2041</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1395</v>
+        <v>0.1322</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8139</v>
+        <v>0.8101</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2914</v>
+        <v>0.3485</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5727</v>
+        <v>0.6317</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2813</v>
+        <v>-0.2832</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9614</v>
+        <v>-2.4345</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2353</v>
+        <v>0.1964</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7262</v>
+        <v>-2.6308</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.2399</v>
+        <v>-3.2429</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.2208</v>
+        <v>-4.2137</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9808</v>
+        <v>0.9708</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2716</v>
+        <v>0.2408</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.2205</v>
+        <v>-2.231</v>
       </c>
       <c r="L11" t="n">
-        <v>2.4921</v>
+        <v>2.4719</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.5115</v>
+        <v>-3.4838</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.0002</v>
+        <v>-1.9827</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4947</v>
+        <v>-0.9639</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6261</v>
+        <v>-0.1535</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8686</v>
+        <v>-0.8104</v>
       </c>
       <c r="V11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4379</v>
+        <v>-4.4364</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3438</v>
+        <v>-2.5635</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0941</v>
+        <v>-1.8729</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5728</v>
+        <v>-2.5713</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.2049</v>
+        <v>-2.2003</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3679</v>
+        <v>-0.3711</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8367</v>
+        <v>-0.864</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6447000000000001</v>
+        <v>-0.6625</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.192</v>
+        <v>-0.2015</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7361</v>
+        <v>-1.7073</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5602</v>
+        <v>-1.5378</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6895</v>
+        <v>-0.6783</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9043</v>
+        <v>-0.077</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7852</v>
+        <v>-0.6012</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W12" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.0263</v>
+        <v>12.0314</v>
       </c>
       <c r="E13" t="n">
-        <v>23.3989</v>
+        <v>23.1006</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.3726</v>
+        <v>-11.0689</v>
       </c>
       <c r="G13" t="n">
-        <v>9.961599999999997</v>
+        <v>10.008</v>
       </c>
       <c r="H13" t="n">
-        <v>-8.1104</v>
+        <v>-8.045500000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>18.0721</v>
+        <v>18.0534</v>
       </c>
       <c r="J13" t="n">
-        <v>24.4205</v>
+        <v>24.1927</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7103</v>
+        <v>3.5964</v>
       </c>
       <c r="L13" t="n">
-        <v>20.7102</v>
+        <v>20.5962</v>
       </c>
       <c r="M13" t="n">
-        <v>-14.4589</v>
+        <v>-14.1847</v>
       </c>
       <c r="N13" t="n">
-        <v>-11.8206</v>
+        <v>-11.6419</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.6381</v>
+        <v>-2.5431</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.8783</v>
+        <v>-15.9342</v>
       </c>
       <c r="R13" t="n">
-        <v>12.4759</v>
+        <v>12.5199</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.6314</v>
+        <v>-2.6467</v>
       </c>
       <c r="T13" t="n">
-        <v>4.2191</v>
+        <v>4.2481</v>
       </c>
       <c r="U13" t="n">
-        <v>-6.850499999999999</v>
+        <v>-6.8948</v>
       </c>
       <c r="V13" t="n">
-        <v>8.098600000000001</v>
+        <v>8.0848</v>
       </c>
       <c r="W13" t="n">
-        <v>10.6376</v>
+        <v>10.5941</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.5392</v>
+        <v>-2.5095</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Y. NZOSA</t>
+          <t>G. CORBALAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5299</v>
+        <v>2.2952</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0176</v>
+        <v>4.283</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5123</v>
+        <v>-1.9878</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7559</v>
+        <v>-0.5961</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5613</v>
+        <v>3.7092</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1946</v>
+        <v>-4.3052</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6305</v>
+        <v>3.6441</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5931</v>
+        <v>5.0602</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0373</v>
+        <v>-1.4161</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1255</v>
+        <v>-4.2401</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0318</v>
+        <v>-1.351</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1573</v>
+        <v>-2.8891</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6805</v>
+        <v>2.5039</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2276</v>
+        <v>0.6652</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5213</v>
+        <v>0.9169</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2937</v>
+        <v>-0.2516</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.8603</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.8603</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. CORBALAN</t>
+          <t>Y. NZOSA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1123</v>
+        <v>1.8507</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2362</v>
+        <v>1.3023</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.1239</v>
+        <v>0.5484</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5662</v>
+        <v>1.7521</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7333</v>
+        <v>1.5569</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.2995</v>
+        <v>0.1952</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7102</v>
+        <v>1.623</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1044</v>
+        <v>1.5858</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.3942</v>
+        <v>0.0372</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.2764</v>
+        <v>0.129</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3711</v>
+        <v>-0.0289</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.9053</v>
+        <v>0.1579</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4952</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4497</v>
+        <v>0.5538</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7924</v>
+        <v>0.8174</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3427</v>
+        <v>-0.2636</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8678</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8678</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6971</v>
+        <v>1.7096</v>
       </c>
       <c r="E16" t="n">
-        <v>4.2257</v>
+        <v>4.2028</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.5286</v>
+        <v>-2.4932</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5129</v>
+        <v>-0.5158</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3983</v>
+        <v>-0.3964</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1147</v>
+        <v>-0.1194</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9645</v>
+        <v>2.935</v>
       </c>
       <c r="K16" t="n">
-        <v>0.547</v>
+        <v>0.5376</v>
       </c>
       <c r="L16" t="n">
-        <v>2.4175</v>
+        <v>2.3974</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.4774</v>
+        <v>-3.4508</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9453</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.5321</v>
+        <v>-2.5168</v>
       </c>
       <c r="P16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1705</v>
+        <v>1.1752</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2612</v>
+        <v>1.2678</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0907</v>
+        <v>-0.0926</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. HAPP</t>
+          <t>P. ALMAZAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4651</v>
+        <v>1.0379</v>
       </c>
       <c r="E17" t="n">
-        <v>4.9115</v>
+        <v>1.4277</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.4465</v>
+        <v>-0.3898</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3737</v>
+        <v>-0.8447</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7406</v>
+        <v>-0.6289</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.3668</v>
+        <v>-0.2158</v>
       </c>
       <c r="J17" t="n">
-        <v>4.0857</v>
+        <v>0.6288</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7423</v>
+        <v>-0.6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3434</v>
+        <v>1.2288</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.7119</v>
+        <v>-1.4734</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0017</v>
+        <v>-0.0289</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.7103</v>
+        <v>-1.4446</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3823</v>
+        <v>0.7444</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0657</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3166</v>
+        <v>-0.0545</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6105</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0285</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. ALMAZAN</t>
+          <t>J. RUBIO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1064</v>
+        <v>0.4632</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6669</v>
+        <v>-0.2953</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5605</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8489</v>
+        <v>-0.431</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6277</v>
+        <v>-0.784</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2212</v>
+        <v>0.3531</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6356000000000001</v>
+        <v>-0.7179</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5959</v>
+        <v>-0.7552</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2315</v>
+        <v>0.0372</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4844</v>
+        <v>0.287</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4526</v>
+        <v>0.3159</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.2113</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0313</v>
+        <v>0.4226</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2102</v>
+        <v>-0.2113</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. RUBIO</t>
+          <t>E. HAPP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.2129</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7658</v>
+        <v>4.1495</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6904</v>
+        <v>-3.9366</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4317</v>
+        <v>0.3656</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7835</v>
+        <v>2.7155</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3519</v>
+        <v>-2.3499</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7144</v>
+        <v>4.0425</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7517</v>
+        <v>2.702</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0373</v>
+        <v>1.3405</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2828</v>
+        <v>-3.6769</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0318</v>
+        <v>0.0135</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3145</v>
+        <v>-3.6904</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3242</v>
+        <v>1.1463</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0514</v>
+        <v>1.3653</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2728</v>
+        <v>-0.219</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6162</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.018</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.72</v>
+        <v>-2.1523</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0601</v>
+        <v>-0.4192</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7801</v>
+        <v>-1.7331</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6977</v>
+        <v>-1.6956</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1832</v>
+        <v>-1.1833</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5144</v>
+        <v>-0.5123</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4</v>
+        <v>-0.4049</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4747</v>
+        <v>-0.4794</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2976</v>
+        <v>-1.2907</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7086</v>
+        <v>-0.7039</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>0.163</v>
+        <v>-0.2777</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2994</v>
+        <v>-0.1721</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1364</v>
+        <v>-0.1057</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="21">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7287</v>
+        <v>-2.2836</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0475</v>
+        <v>-0.7078</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6812</v>
+        <v>-1.5758</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1074</v>
+        <v>-2.1131</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0304</v>
+        <v>0.0261</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1378</v>
+        <v>-2.1391</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8389</v>
+        <v>-0.8541</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0622</v>
+        <v>0.055</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.901</v>
+        <v>-0.909</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2685</v>
+        <v>-1.259</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2368</v>
+        <v>-1.2301</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2092,22 +2092,22 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4606</v>
+        <v>-0.0128</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2087</v>
+        <v>0.1462</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2519</v>
+        <v>-0.159</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9535</v>
+        <v>-2.3217</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5275</v>
+        <v>0.9705</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4809</v>
+        <v>-3.2922</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0001</v>
+        <v>0.9969</v>
       </c>
       <c r="H22" t="n">
-        <v>2.2395</v>
+        <v>2.2347</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2395</v>
+        <v>-1.2378</v>
       </c>
       <c r="J22" t="n">
-        <v>2.4067</v>
+        <v>2.3847</v>
       </c>
       <c r="K22" t="n">
-        <v>2.0363</v>
+        <v>2.02</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3705</v>
+        <v>0.3647</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4066</v>
+        <v>-1.3877</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6099</v>
+        <v>-1.6025</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5167</v>
+        <v>-0.8909</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5202</v>
+        <v>-0.0468</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9966</v>
+        <v>-0.8441</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.1173</v>
+        <v>-3.1107</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3495</v>
+        <v>-2.5714</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0596</v>
+        <v>-0.38</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2899</v>
+        <v>-2.1914</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5573</v>
+        <v>0.5621</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4156</v>
+        <v>-0.4137</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9729</v>
+        <v>0.9758</v>
       </c>
       <c r="J23" t="n">
-        <v>1.7289</v>
+        <v>1.7062</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0897</v>
+        <v>0.0755</v>
       </c>
       <c r="L23" t="n">
-        <v>1.6392</v>
+        <v>1.6308</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1716</v>
+        <v>-1.1441</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.041</v>
+        <v>-0.2717</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5202</v>
+        <v>0.1901</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5208</v>
+        <v>-0.4618</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.1124</v>
+        <v>-4.0109</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3231</v>
+        <v>-2.1227</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7893</v>
+        <v>-1.8882</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.8237</v>
+        <v>-4.8294</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0951</v>
+        <v>-0.103</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.7286</v>
+        <v>-4.7265</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.0231</v>
+        <v>-2.0536</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.2984</v>
+        <v>-0.3177</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.7247</v>
+        <v>-1.7359</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.8007</v>
+        <v>-2.7758</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.0039</v>
+        <v>-2.9906</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6763</v>
+        <v>-0.5669</v>
       </c>
       <c r="T24" t="n">
-        <v>0.127</v>
+        <v>0.3665</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8033</v>
+        <v>-0.9334</v>
       </c>
       <c r="V24" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W24" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.9976</v>
+        <v>-6.261</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.0769</v>
+        <v>-1.3416</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.9207</v>
+        <v>-4.9194</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.6603</v>
+        <v>-2.6591</v>
       </c>
       <c r="H25" t="n">
-        <v>1.3087</v>
+        <v>1.3123</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.969</v>
+        <v>-3.9714</v>
       </c>
       <c r="J25" t="n">
-        <v>1.2731</v>
+        <v>1.2511</v>
       </c>
       <c r="K25" t="n">
-        <v>1.7663</v>
+        <v>1.7582</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.4932</v>
+        <v>-0.5071</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.9334</v>
+        <v>-3.9102</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.4758</v>
+        <v>-3.4643</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4358</v>
+        <v>0.1705</v>
       </c>
       <c r="T25" t="n">
-        <v>1.0525</v>
+        <v>0.8218</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6167</v>
+        <v>-0.6513</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-12.0263</v>
+        <v>-12.0314</v>
       </c>
       <c r="E26" t="n">
-        <v>11.3726</v>
+        <v>11.0692</v>
       </c>
       <c r="F26" t="n">
-        <v>-23.3989</v>
+        <v>-23.1005</v>
       </c>
       <c r="G26" t="n">
-        <v>-9.961799999999998</v>
+        <v>-10.0081</v>
       </c>
       <c r="H26" t="n">
-        <v>8.110399999999998</v>
+        <v>8.045400000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-18.0721</v>
+        <v>-18.0533</v>
       </c>
       <c r="J26" t="n">
-        <v>14.4588</v>
+        <v>14.1849</v>
       </c>
       <c r="K26" t="n">
-        <v>11.8206</v>
+        <v>11.642</v>
       </c>
       <c r="L26" t="n">
-        <v>2.6382</v>
+        <v>2.543</v>
       </c>
       <c r="M26" t="n">
-        <v>-24.4202</v>
+        <v>-24.19269999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>-3.7102</v>
+        <v>-3.5963</v>
       </c>
       <c r="O26" t="n">
-        <v>-20.7103</v>
+        <v>-20.5963</v>
       </c>
       <c r="P26" t="n">
-        <v>3.402500000000001</v>
+        <v>3.4145</v>
       </c>
       <c r="Q26" t="n">
-        <v>-12.4759</v>
+        <v>-12.5199</v>
       </c>
       <c r="R26" t="n">
-        <v>15.8784</v>
+        <v>15.9343</v>
       </c>
       <c r="S26" t="n">
-        <v>2.6312</v>
+        <v>2.6467</v>
       </c>
       <c r="T26" t="n">
-        <v>6.8503</v>
+        <v>6.894600000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.2192</v>
+        <v>-4.2479</v>
       </c>
       <c r="V26" t="n">
-        <v>-8.0983</v>
+        <v>-8.0847</v>
       </c>
       <c r="W26" t="n">
-        <v>2.5392</v>
+        <v>2.5094</v>
       </c>
       <c r="X26" t="n">
-        <v>-10.6375</v>
+        <v>-10.5939</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104660_W23.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104660_W23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-2.5095</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104660_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-10.5939</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
